--- a/Saprotrophs.xlsx
+++ b/Saprotrophs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaseamus/Desktop/PhD/Papers/Microbial decomposition/microdeco/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D74D472B-513A-4740-A8F6-F9291309EFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232EA0A3-F321-4C4C-81B6-3CFA4E8C3DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{66FE6731-E709-924C-9370-CCE9A242822C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19020" xr2:uid="{66FE6731-E709-924C-9370-CCE9A242822C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7623" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8848" uniqueCount="987">
   <si>
     <t>Reference</t>
   </si>
@@ -1793,9 +1793,6 @@
     <t>Goecke et al. 2013</t>
   </si>
   <si>
-    <t>Lavin et al. 2013</t>
-  </si>
-  <si>
     <t>Ibrahim et al. 2015</t>
   </si>
   <si>
@@ -2310,6 +2307,696 @@
   </si>
   <si>
     <t>Figure 1b, 3</t>
+  </si>
+  <si>
+    <t>Saccharina japonica, alginate, starch, agar, xylan</t>
+  </si>
+  <si>
+    <t>Xia et al. 2023</t>
+  </si>
+  <si>
+    <t>10.3389/fmars.2023.985514</t>
+  </si>
+  <si>
+    <t>Figure 6, Table 2, Text</t>
+  </si>
+  <si>
+    <t>Martin et al. 2015</t>
+  </si>
+  <si>
+    <t>10.3389/fmicb.2015.01487</t>
+  </si>
+  <si>
+    <t>carrageenan, alginate, Pelvetia canaliculata fucoidan, Ascophyllum nodosum fucoidan, laminarin</t>
+  </si>
+  <si>
+    <t>10.3389/fmicb.2018.02740</t>
+  </si>
+  <si>
+    <t>Gobet et al. 2018</t>
+  </si>
+  <si>
+    <t>seawater, seaweed</t>
+  </si>
+  <si>
+    <t>Figure 4</t>
+  </si>
+  <si>
+    <t>alginate, ulvan</t>
+  </si>
+  <si>
+    <t>10.3389/fmicb.2019.00504</t>
+  </si>
+  <si>
+    <t>forsetii</t>
+  </si>
+  <si>
+    <t>Laminaria digitata laminarin</t>
+  </si>
+  <si>
+    <t>Figure 1, Text</t>
+  </si>
+  <si>
+    <t>Kalenborn et al. 2024</t>
+  </si>
+  <si>
+    <t>10.3389/fmicb.2024.1393588</t>
+  </si>
+  <si>
+    <t>Johansen et al. 1999</t>
+  </si>
+  <si>
+    <t>Jain &amp; Krishnan 2017</t>
+  </si>
+  <si>
+    <t>10.1007/s13213-016-1252-0</t>
+  </si>
+  <si>
+    <t>Undaria pinnatifida fucoidan</t>
+  </si>
+  <si>
+    <t>seawater, sediment, seaweed</t>
+  </si>
+  <si>
+    <t>talitrid amphipod</t>
+  </si>
+  <si>
+    <t>Nakamura et al. 2022</t>
+  </si>
+  <si>
+    <t>10.1371/journal.pone.0279834</t>
+  </si>
+  <si>
+    <t>furnissii</t>
+  </si>
+  <si>
+    <t>Zhu et al. 2018</t>
+  </si>
+  <si>
+    <t>Sun et al. 2022</t>
+  </si>
+  <si>
+    <t>10.3390/md20040254</t>
+  </si>
+  <si>
+    <t>10.3390/md16010030</t>
+  </si>
+  <si>
+    <t>Haliotis discus hannai</t>
+  </si>
+  <si>
+    <t>alginate, agar, carrageenan, starch</t>
+  </si>
+  <si>
+    <t>Figure 1, 2a, 6a, Text</t>
+  </si>
+  <si>
+    <t>Gong et al. 2024</t>
+  </si>
+  <si>
+    <t>10.3390/md22050203</t>
+  </si>
+  <si>
+    <t>Saccharina japonica, Sargassum, alginate, laminarin</t>
+  </si>
+  <si>
+    <t>Figure 1, 3a, 4, Text</t>
+  </si>
+  <si>
+    <t>seaweed-eating sheep</t>
+  </si>
+  <si>
+    <t>Prevotella</t>
+  </si>
+  <si>
+    <t>Clostridium</t>
+  </si>
+  <si>
+    <t>butyricum</t>
+  </si>
+  <si>
+    <t>Table 1, Figure 1, Text</t>
+  </si>
+  <si>
+    <t>Laminaria hyperborea, alginate, laminarin, fucoidan, cellulose, Fucus, Ascophyllum nodosum, xylan, carrageenan, pectin</t>
+  </si>
+  <si>
+    <t>10.1002/mbo3.10</t>
+  </si>
+  <si>
+    <t>Sakatoku et al. 2012</t>
+  </si>
+  <si>
+    <t>Figure 1, 3, 4, Table 1</t>
+  </si>
+  <si>
+    <t>Undaria pinnatifida, Gelidium, Ulva, alginate, cellulose, fucoidan, laminarin, carrageenan, pectin, xylan, starch, agar</t>
+  </si>
+  <si>
+    <t>Wang et al. 2016</t>
+  </si>
+  <si>
+    <t>10.1002/mbo3.387</t>
+  </si>
+  <si>
+    <t>decayed Saccharina japonica</t>
+  </si>
+  <si>
+    <t>Sargassum horneri, alginate</t>
+  </si>
+  <si>
+    <t>Text, Figure 3</t>
+  </si>
+  <si>
+    <t>Nakata et al. 2024</t>
+  </si>
+  <si>
+    <t>algivorus</t>
+  </si>
+  <si>
+    <t>Figure 3, Text</t>
+  </si>
+  <si>
+    <t>faecale</t>
+  </si>
+  <si>
+    <t>Figure 4, Text</t>
+  </si>
+  <si>
+    <t>decayed Porphyra</t>
+  </si>
+  <si>
+    <t>Lavín et al. 2016</t>
+  </si>
+  <si>
+    <t>Lavín et al. 2013</t>
+  </si>
+  <si>
+    <t>10.1515/popore-2016-0021</t>
+  </si>
+  <si>
+    <t>cellulose, Sargassum</t>
+  </si>
+  <si>
+    <t>10.1080/10498850.2012.670836</t>
+  </si>
+  <si>
+    <t>Shobharani et al. 2013</t>
+  </si>
+  <si>
+    <t>Figure 3, 4, 8, Text</t>
+  </si>
+  <si>
+    <t>Valdehuesa et al. 2018</t>
+  </si>
+  <si>
+    <t>10.1007/s00284-018-1467-3</t>
+  </si>
+  <si>
+    <t>Chryseobacterium</t>
+  </si>
+  <si>
+    <t>barbadense</t>
+  </si>
+  <si>
+    <t>daecheongense</t>
+  </si>
+  <si>
+    <t>10.1007/s00284-025-04701-4</t>
+  </si>
+  <si>
+    <t>Sakai et al. 2002</t>
+  </si>
+  <si>
+    <t>10.1007/s10126-002-0032-y</t>
+  </si>
+  <si>
+    <t>Kjellmaniella crassifolia fucoidan</t>
+  </si>
+  <si>
+    <t>Imran et al. 2017</t>
+  </si>
+  <si>
+    <t>10.1007/s10126-017-9737-9</t>
+  </si>
+  <si>
+    <t>mangrovi</t>
+  </si>
+  <si>
+    <t>agar, alginate, Gracilaria corticata, Sargassum tenerrimum, carrageenan, xylan, cellulose, pectin, starch</t>
+  </si>
+  <si>
+    <t>Vashist et al. 2013</t>
+  </si>
+  <si>
+    <t>10.1099/ijs.0.042978-0</t>
+  </si>
+  <si>
+    <t>seawater in mangrove forest</t>
+  </si>
+  <si>
+    <t>Figure 2, 3, Text</t>
+  </si>
+  <si>
+    <t>pectin, alginate, laminarin, carrageenan</t>
+  </si>
+  <si>
+    <t>hydrolyticus</t>
+  </si>
+  <si>
+    <t>celer</t>
+  </si>
+  <si>
+    <t>agarilyticus</t>
+  </si>
+  <si>
+    <t>pectin, alginate, carrageenan</t>
+  </si>
+  <si>
+    <t>pulp mill waste</t>
+  </si>
+  <si>
+    <t>saltern</t>
+  </si>
+  <si>
+    <t>Wakabayashi et al. 2012</t>
+  </si>
+  <si>
+    <t>10.1007/s10532-011-9489-6</t>
+  </si>
+  <si>
+    <t>Table 1, Figure 1, 3, 5</t>
+  </si>
+  <si>
+    <t>agar, alginate, cellulose, Undaria pinnatifida</t>
+  </si>
+  <si>
+    <t>drifting seaweed</t>
+  </si>
+  <si>
+    <t>Zeb et al. 2024</t>
+  </si>
+  <si>
+    <t>10.1007/s11033-024-09724-x</t>
+  </si>
+  <si>
+    <t>elongata</t>
+  </si>
+  <si>
+    <t>agar, cellulose, starch, Neopyropia yezoensis</t>
+  </si>
+  <si>
+    <t>Text, Figure 6, 8</t>
+  </si>
+  <si>
+    <t>10.1007/s11274-014-1778-x</t>
+  </si>
+  <si>
+    <t>Kang &amp; Kim 2015</t>
+  </si>
+  <si>
+    <t>Text, Table 1, Figure 1</t>
+  </si>
+  <si>
+    <t>agar, carrageenan, Rhodophyta</t>
+  </si>
+  <si>
+    <t>10.1007/s11802-014-2011-0</t>
+  </si>
+  <si>
+    <t>Saccharina japonica fucoidan</t>
+  </si>
+  <si>
+    <t>kelp</t>
+  </si>
+  <si>
+    <t>Text, Figure 2, 4</t>
+  </si>
+  <si>
+    <t>Turbo cornutus</t>
+  </si>
+  <si>
+    <t>Gomare et al. 2011</t>
+  </si>
+  <si>
+    <t>10.1007/s11814-010-0506-y</t>
+  </si>
+  <si>
+    <t>Text, Table 1, Figure 5</t>
+  </si>
+  <si>
+    <t>cellulose, laminarin, alginate, Saccharina japonica</t>
+  </si>
+  <si>
+    <t>Li et al. 2011</t>
+  </si>
+  <si>
+    <t>10.1007/s12010-010-9136-4</t>
+  </si>
+  <si>
+    <t>fluorescens</t>
+  </si>
+  <si>
+    <t>Tawara et al. 2015</t>
+  </si>
+  <si>
+    <t>10.1007/s12010-015-1765-1</t>
+  </si>
+  <si>
+    <t>Simiduia</t>
+  </si>
+  <si>
+    <t>Undaria pinnatifida, Ulva, Gelidium, agar, alginate, cellulose</t>
+  </si>
+  <si>
+    <t>Saravanan et al. 2024</t>
+  </si>
+  <si>
+    <t>10.1007/s12088-024-01205-w</t>
+  </si>
+  <si>
+    <t>Kappaphycus alvarezii, Gracilaria edulis, Kappaphycopsis cottonii</t>
+  </si>
+  <si>
+    <t>Table 1, Figure 9</t>
+  </si>
+  <si>
+    <t>kokeshiiformis</t>
+  </si>
+  <si>
+    <t>Caldibacillus</t>
+  </si>
+  <si>
+    <t>Lentibacillus</t>
+  </si>
+  <si>
+    <t>salarius</t>
+  </si>
+  <si>
+    <t>Petchimuthu et al. 2024</t>
+  </si>
+  <si>
+    <t>10.1007/s12223-024-01150-7</t>
+  </si>
+  <si>
+    <t>tabaci</t>
+  </si>
+  <si>
+    <t>Ramya et al. 2023</t>
+  </si>
+  <si>
+    <t>10.1007/s10499-023-01302-5</t>
+  </si>
+  <si>
+    <t>sponge, seaweed</t>
+  </si>
+  <si>
+    <t>Text, Figure 2</t>
+  </si>
+  <si>
+    <t>Sargassum swartzii, alginate</t>
+  </si>
+  <si>
+    <t>Jegatheesan et al. 2017</t>
+  </si>
+  <si>
+    <t>10.1007/s13399-016-0212-z</t>
+  </si>
+  <si>
+    <t>10.1128/aem.00914-23</t>
+  </si>
+  <si>
+    <t>Pontiella</t>
+  </si>
+  <si>
+    <t>carrageenan, xylan, agar</t>
+  </si>
+  <si>
+    <t>desulfatans</t>
+  </si>
+  <si>
+    <t>sulfatireligans</t>
+  </si>
+  <si>
+    <t>fucoidan, carrageenan</t>
+  </si>
+  <si>
+    <t>Mohapatra 2021</t>
+  </si>
+  <si>
+    <t>10.1007/s13399-020-00658-5</t>
+  </si>
+  <si>
+    <t>Sargassum fluitans, Sargassum natans</t>
+  </si>
+  <si>
+    <t>alginate, Sargassum fluitans, Sargassum natans</t>
+  </si>
+  <si>
+    <t>natto</t>
+  </si>
+  <si>
+    <t>Hung et al. 2025</t>
+  </si>
+  <si>
+    <t>10.1186/s40643-025-00912-6</t>
+  </si>
+  <si>
+    <t>alginate, cellulose, Saccharina japonica</t>
+  </si>
+  <si>
+    <t>10.1038/s41396-018-0252-4</t>
+  </si>
+  <si>
+    <t>Laminaria digitata laminarin, alginate, pectin</t>
+  </si>
+  <si>
+    <t>Pérez-Cruz et al. 2024</t>
+  </si>
+  <si>
+    <t>10.1038/s41467-024-55268-w</t>
+  </si>
+  <si>
+    <t>gimesia</t>
+  </si>
+  <si>
+    <t>Neorhodopirellula</t>
+  </si>
+  <si>
+    <t>lusitana</t>
+  </si>
+  <si>
+    <t>Fucus vesiculosus fucoidan, Undaria pinnatifida fucoidan, laminarin</t>
+  </si>
+  <si>
+    <t>Hettle et al. 2019</t>
+  </si>
+  <si>
+    <t>10.1038/s42003-019-0721-y</t>
+  </si>
+  <si>
+    <t>Fucus</t>
+  </si>
+  <si>
+    <t>Figure 2a, Table S1</t>
+  </si>
+  <si>
+    <t>fuliginea</t>
+  </si>
+  <si>
+    <t>weihaiensis</t>
+  </si>
+  <si>
+    <t>Zhu et al. 2016</t>
+  </si>
+  <si>
+    <t>10.1038/srep38248</t>
+  </si>
+  <si>
+    <t>decayed Sargassum fusiforme</t>
+  </si>
+  <si>
+    <t>Cheng et al. 2020</t>
+  </si>
+  <si>
+    <t>10.1038/s41598-020-67921-7</t>
+  </si>
+  <si>
+    <t>Chen et al. 2018</t>
+  </si>
+  <si>
+    <t>10.3390/md16030086</t>
+  </si>
+  <si>
+    <t>decayed kelp, sediment</t>
+  </si>
+  <si>
+    <t>Mohapatra 2025</t>
+  </si>
+  <si>
+    <t>Wang et al. 2014</t>
+  </si>
+  <si>
+    <t>agar, carrageenan, alginate</t>
+  </si>
+  <si>
+    <t>carrageenan, alginate</t>
+  </si>
+  <si>
+    <t>ushuaiensis</t>
+  </si>
+  <si>
+    <t>10.1099/00207713-49-3-1231</t>
+  </si>
+  <si>
+    <t>marinoflava</t>
+  </si>
+  <si>
+    <t>agar, carrageenan, cellulose, starch</t>
+  </si>
+  <si>
+    <t>carrageenan, starch</t>
+  </si>
+  <si>
+    <t>agar, alginate, carrageenan, cellulose, starch</t>
+  </si>
+  <si>
+    <t>flevense</t>
+  </si>
+  <si>
+    <t>agar, carrageenan, cellulose</t>
+  </si>
+  <si>
+    <t>Table 1, 3, Text</t>
+  </si>
+  <si>
+    <t>orientalis</t>
+  </si>
+  <si>
+    <t>grimontii</t>
+  </si>
+  <si>
+    <t>extremaustralis</t>
+  </si>
+  <si>
+    <t>mandelii</t>
+  </si>
+  <si>
+    <t>cryohalolentis</t>
+  </si>
+  <si>
+    <t>fozii</t>
+  </si>
+  <si>
+    <t>vesiculosa</t>
+  </si>
+  <si>
+    <t>mandellii</t>
+  </si>
+  <si>
+    <t>luti</t>
+  </si>
+  <si>
+    <t>alimentarius</t>
+  </si>
+  <si>
+    <t>Table 2, Text</t>
+  </si>
+  <si>
+    <t>alginate, starch, pectin, xylan, cellulose</t>
+  </si>
+  <si>
+    <t>starch, pectin, alginate, xylan</t>
+  </si>
+  <si>
+    <t>starch, alginate, pectin</t>
+  </si>
+  <si>
+    <t>alginate, pectin, starch, xylan</t>
+  </si>
+  <si>
+    <t>pectin, alginate, xylan, starch</t>
+  </si>
+  <si>
+    <t>starch, pectin, alginate, xylan, cellulose</t>
+  </si>
+  <si>
+    <t>pectin, alginate, starch, xylan, cellulose</t>
+  </si>
+  <si>
+    <t>xylan, cellulose, pectin, alginate</t>
+  </si>
+  <si>
+    <t>alginate, starch, pectin</t>
+  </si>
+  <si>
+    <t>pectin, alginate, xylan</t>
+  </si>
+  <si>
+    <t>pectin, xylan, cellulose</t>
+  </si>
+  <si>
+    <t>Table 3, Figure 2, Text</t>
+  </si>
+  <si>
+    <t>fistulariae</t>
+  </si>
+  <si>
+    <t>homiensis</t>
+  </si>
+  <si>
+    <t>chemaguriensis</t>
+  </si>
+  <si>
+    <t>10.1128/aem.00255-24</t>
+  </si>
+  <si>
+    <t>10.1111/1751-7915.12000</t>
+  </si>
+  <si>
+    <t>10.1128/aem.01683-24</t>
+  </si>
+  <si>
+    <t>omnivescoria</t>
+  </si>
+  <si>
+    <t>Rhodophyta</t>
+  </si>
+  <si>
+    <t>agar, alginate, starch</t>
+  </si>
+  <si>
+    <t>Sinomicrobium</t>
+  </si>
+  <si>
+    <t>decayed Anthophycus longifolius</t>
+  </si>
+  <si>
+    <t>alginate, Sargassum wightii</t>
+  </si>
+  <si>
+    <t>Table S1, Figure 1, Table 1</t>
+  </si>
+  <si>
+    <t>alginate, laminarin, kelp</t>
+  </si>
+  <si>
+    <t>Kim et al. 2008</t>
+  </si>
+  <si>
+    <t>Williams et al. 2013</t>
+  </si>
+  <si>
+    <t>Koch et al. 2019a</t>
+  </si>
+  <si>
+    <t>Liu et al. 2024a</t>
+  </si>
+  <si>
+    <t>Liu et al. 2024b</t>
+  </si>
+  <si>
+    <t>Koch et al. 2019b</t>
   </si>
 </sst>
 </file>
@@ -2319,7 +3006,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2350,6 +3037,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2371,7 +3064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2392,6 +3085,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2726,11 +3420,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B2102F-A492-4646-A482-3DC7C29DBCFC}">
-  <dimension ref="A1:AB1089"/>
+  <dimension ref="A1:AB1264"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="31.1640625" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" customWidth="1"/>
@@ -2802,7 +3496,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -2825,7 +3519,7 @@
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -2917,7 +3611,7 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -2986,7 +3680,7 @@
         <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -3782,16 +4476,16 @@
         <v>71</v>
       </c>
       <c r="C46" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D46" t="s">
         <v>70</v>
       </c>
       <c r="E46" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F46" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G46" t="s">
         <v>68</v>
@@ -6197,7 +6891,7 @@
         <v>177</v>
       </c>
       <c r="C151" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D151" t="s">
         <v>171</v>
@@ -6220,7 +6914,7 @@
         <v>177</v>
       </c>
       <c r="C152" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D152" t="s">
         <v>172</v>
@@ -6243,7 +6937,7 @@
         <v>177</v>
       </c>
       <c r="C153" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D153" t="s">
         <v>173</v>
@@ -6266,7 +6960,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D154" t="s">
         <v>174</v>
@@ -6289,7 +6983,7 @@
         <v>177</v>
       </c>
       <c r="C155" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D155" t="s">
         <v>175</v>
@@ -6312,7 +7006,7 @@
         <v>177</v>
       </c>
       <c r="C156" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D156" t="s">
         <v>179</v>
@@ -6335,7 +7029,7 @@
         <v>177</v>
       </c>
       <c r="C157" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D157" t="s">
         <v>180</v>
@@ -6358,7 +7052,7 @@
         <v>177</v>
       </c>
       <c r="C158" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D158" t="s">
         <v>181</v>
@@ -6381,7 +7075,7 @@
         <v>188</v>
       </c>
       <c r="C159" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D159" t="s">
         <v>57</v>
@@ -6404,7 +7098,7 @@
         <v>188</v>
       </c>
       <c r="C160" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D160" t="s">
         <v>182</v>
@@ -6427,7 +7121,7 @@
         <v>188</v>
       </c>
       <c r="C161" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D161" t="s">
         <v>183</v>
@@ -6450,7 +7144,7 @@
         <v>188</v>
       </c>
       <c r="C162" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D162" t="s">
         <v>174</v>
@@ -6473,7 +7167,7 @@
         <v>188</v>
       </c>
       <c r="C163" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D163" t="s">
         <v>184</v>
@@ -6496,7 +7190,7 @@
         <v>188</v>
       </c>
       <c r="C164" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D164" t="s">
         <v>185</v>
@@ -6519,7 +7213,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D165" t="s">
         <v>79</v>
@@ -6551,7 +7245,7 @@
         <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G166" t="s">
         <v>193</v>
@@ -6574,7 +7268,7 @@
         <v>21</v>
       </c>
       <c r="F167" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G167" t="s">
         <v>193</v>
@@ -6597,7 +7291,7 @@
         <v>21</v>
       </c>
       <c r="F168" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G168" t="s">
         <v>193</v>
@@ -6620,7 +7314,7 @@
         <v>21</v>
       </c>
       <c r="F169" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G169" t="s">
         <v>193</v>
@@ -6643,7 +7337,7 @@
         <v>192</v>
       </c>
       <c r="F170" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G170" t="s">
         <v>193</v>
@@ -6758,7 +7452,7 @@
         <v>63</v>
       </c>
       <c r="F175" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G175" t="s">
         <v>68</v>
@@ -6772,7 +7466,7 @@
         <v>204</v>
       </c>
       <c r="C176" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D176" t="s">
         <v>202</v>
@@ -12062,7 +12756,7 @@
         <v>222</v>
       </c>
       <c r="C406" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D406" t="s">
         <v>381</v>
@@ -12085,7 +12779,7 @@
         <v>222</v>
       </c>
       <c r="C407" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D407" t="s">
         <v>51</v>
@@ -12131,7 +12825,7 @@
         <v>222</v>
       </c>
       <c r="C409" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D409" t="s">
         <v>62</v>
@@ -12154,7 +12848,7 @@
         <v>222</v>
       </c>
       <c r="C410" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D410" t="s">
         <v>79</v>
@@ -12223,7 +12917,7 @@
         <v>222</v>
       </c>
       <c r="C413" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D413" t="s">
         <v>381</v>
@@ -12246,7 +12940,7 @@
         <v>222</v>
       </c>
       <c r="C414" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D414" t="s">
         <v>51</v>
@@ -12269,7 +12963,7 @@
         <v>222</v>
       </c>
       <c r="C415" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D415" t="s">
         <v>79</v>
@@ -12292,7 +12986,7 @@
         <v>222</v>
       </c>
       <c r="C416" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D416" t="s">
         <v>98</v>
@@ -12476,7 +13170,7 @@
         <v>222</v>
       </c>
       <c r="C424" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D424" t="s">
         <v>57</v>
@@ -12499,7 +13193,7 @@
         <v>222</v>
       </c>
       <c r="C425" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D425" t="s">
         <v>51</v>
@@ -12545,7 +13239,7 @@
         <v>222</v>
       </c>
       <c r="C427" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D427" t="s">
         <v>392</v>
@@ -12614,7 +13308,7 @@
         <v>222</v>
       </c>
       <c r="C430" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D430" t="s">
         <v>392</v>
@@ -12646,7 +13340,7 @@
         <v>63</v>
       </c>
       <c r="F431" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G431" t="s">
         <v>221</v>
@@ -12660,7 +13354,7 @@
         <v>222</v>
       </c>
       <c r="C432" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D432" t="s">
         <v>395</v>
@@ -12798,7 +13492,7 @@
         <v>222</v>
       </c>
       <c r="C438" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D438" t="s">
         <v>51</v>
@@ -12821,7 +13515,7 @@
         <v>222</v>
       </c>
       <c r="C439" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D439" t="s">
         <v>401</v>
@@ -12844,7 +13538,7 @@
         <v>224</v>
       </c>
       <c r="C440" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D440" t="s">
         <v>51</v>
@@ -12867,7 +13561,7 @@
         <v>224</v>
       </c>
       <c r="C441" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D441" t="s">
         <v>51</v>
@@ -12890,7 +13584,7 @@
         <v>224</v>
       </c>
       <c r="C442" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D442" t="s">
         <v>51</v>
@@ -12913,7 +13607,7 @@
         <v>224</v>
       </c>
       <c r="C443" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D443" t="s">
         <v>51</v>
@@ -12936,7 +13630,7 @@
         <v>224</v>
       </c>
       <c r="C444" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D444" t="s">
         <v>51</v>
@@ -12959,7 +13653,7 @@
         <v>224</v>
       </c>
       <c r="C445" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D445" t="s">
         <v>51</v>
@@ -12982,7 +13676,7 @@
         <v>224</v>
       </c>
       <c r="C446" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D446" t="s">
         <v>51</v>
@@ -13005,7 +13699,7 @@
         <v>224</v>
       </c>
       <c r="C447" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D447" t="s">
         <v>51</v>
@@ -13028,7 +13722,7 @@
         <v>224</v>
       </c>
       <c r="C448" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D448" t="s">
         <v>51</v>
@@ -13051,7 +13745,7 @@
         <v>224</v>
       </c>
       <c r="C449" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D449" t="s">
         <v>51</v>
@@ -13097,7 +13791,7 @@
         <v>224</v>
       </c>
       <c r="C451" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D451" t="s">
         <v>51</v>
@@ -13120,7 +13814,7 @@
         <v>224</v>
       </c>
       <c r="C452" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D452" t="s">
         <v>51</v>
@@ -13143,7 +13837,7 @@
         <v>224</v>
       </c>
       <c r="C453" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D453" t="s">
         <v>51</v>
@@ -13166,7 +13860,7 @@
         <v>224</v>
       </c>
       <c r="C454" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D454" t="s">
         <v>51</v>
@@ -13189,7 +13883,7 @@
         <v>224</v>
       </c>
       <c r="C455" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D455" t="s">
         <v>51</v>
@@ -13212,7 +13906,7 @@
         <v>226</v>
       </c>
       <c r="C456" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D456" t="s">
         <v>79</v>
@@ -13235,7 +13929,7 @@
         <v>226</v>
       </c>
       <c r="C457" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D457" t="s">
         <v>414</v>
@@ -13258,7 +13952,7 @@
         <v>226</v>
       </c>
       <c r="C458" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D458" t="s">
         <v>172</v>
@@ -13281,7 +13975,7 @@
         <v>226</v>
       </c>
       <c r="C459" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D459" t="s">
         <v>79</v>
@@ -13304,7 +13998,7 @@
         <v>226</v>
       </c>
       <c r="C460" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D460" t="s">
         <v>415</v>
@@ -13327,7 +14021,7 @@
         <v>226</v>
       </c>
       <c r="C461" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D461" t="s">
         <v>79</v>
@@ -13350,7 +14044,7 @@
         <v>226</v>
       </c>
       <c r="C462" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D462" t="s">
         <v>79</v>
@@ -13373,7 +14067,7 @@
         <v>226</v>
       </c>
       <c r="C463" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D463" t="s">
         <v>57</v>
@@ -13396,7 +14090,7 @@
         <v>226</v>
       </c>
       <c r="C464" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D464" t="s">
         <v>51</v>
@@ -13419,7 +14113,7 @@
         <v>226</v>
       </c>
       <c r="C465" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D465" t="s">
         <v>79</v>
@@ -13442,7 +14136,7 @@
         <v>226</v>
       </c>
       <c r="C466" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D466" t="s">
         <v>345</v>
@@ -13465,7 +14159,7 @@
         <v>226</v>
       </c>
       <c r="C467" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D467" t="s">
         <v>79</v>
@@ -13488,7 +14182,7 @@
         <v>226</v>
       </c>
       <c r="C468" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D468" t="s">
         <v>79</v>
@@ -13511,7 +14205,7 @@
         <v>226</v>
       </c>
       <c r="C469" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D469" t="s">
         <v>57</v>
@@ -13534,7 +14228,7 @@
         <v>226</v>
       </c>
       <c r="C470" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D470" t="s">
         <v>79</v>
@@ -13557,7 +14251,7 @@
         <v>226</v>
       </c>
       <c r="C471" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D471" t="s">
         <v>423</v>
@@ -13580,7 +14274,7 @@
         <v>226</v>
       </c>
       <c r="C472" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D472" t="s">
         <v>424</v>
@@ -13603,7 +14297,7 @@
         <v>226</v>
       </c>
       <c r="C473" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D473" t="s">
         <v>415</v>
@@ -13626,7 +14320,7 @@
         <v>428</v>
       </c>
       <c r="C474" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D474" t="s">
         <v>345</v>
@@ -29210,7 +29904,7 @@
         <v>505</v>
       </c>
       <c r="C884" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D884" t="s">
         <v>57</v>
@@ -29219,7 +29913,7 @@
         <v>21</v>
       </c>
       <c r="F884" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G884" t="s">
         <v>221</v>
@@ -29233,7 +29927,7 @@
         <v>505</v>
       </c>
       <c r="C885" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D885" t="s">
         <v>114</v>
@@ -29256,7 +29950,7 @@
         <v>505</v>
       </c>
       <c r="C886" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D886" t="s">
         <v>50</v>
@@ -29279,7 +29973,7 @@
         <v>505</v>
       </c>
       <c r="C887" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D887" t="s">
         <v>173</v>
@@ -29302,7 +29996,7 @@
         <v>505</v>
       </c>
       <c r="C888" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D888" t="s">
         <v>51</v>
@@ -29311,7 +30005,7 @@
         <v>21</v>
       </c>
       <c r="F888" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G888" t="s">
         <v>221</v>
@@ -29325,7 +30019,7 @@
         <v>505</v>
       </c>
       <c r="C889" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D889" t="s">
         <v>506</v>
@@ -29348,7 +30042,7 @@
         <v>505</v>
       </c>
       <c r="C890" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D890" t="s">
         <v>507</v>
@@ -29371,7 +30065,7 @@
         <v>505</v>
       </c>
       <c r="C891" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D891" t="s">
         <v>398</v>
@@ -29394,7 +30088,7 @@
         <v>505</v>
       </c>
       <c r="C892" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D892" t="s">
         <v>441</v>
@@ -29417,7 +30111,7 @@
         <v>505</v>
       </c>
       <c r="C893" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D893" t="s">
         <v>508</v>
@@ -30507,7 +31201,7 @@
         <v>561</v>
       </c>
       <c r="F940" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G940" t="s">
         <v>562</v>
@@ -30521,7 +31215,7 @@
         <v>564</v>
       </c>
       <c r="C941" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D941" t="s">
         <v>79</v>
@@ -31113,13 +31807,13 @@
     </row>
     <row r="967" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A967" t="s">
+        <v>598</v>
+      </c>
+      <c r="B967" t="s">
         <v>599</v>
       </c>
-      <c r="B967" t="s">
+      <c r="C967" t="s">
         <v>600</v>
-      </c>
-      <c r="C967" t="s">
-        <v>601</v>
       </c>
       <c r="D967" t="s">
         <v>47</v>
@@ -31128,7 +31822,7 @@
         <v>21</v>
       </c>
       <c r="F967" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G967" t="s">
         <v>43</v>
@@ -31136,13 +31830,13 @@
     </row>
     <row r="968" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A968" t="s">
+        <v>598</v>
+      </c>
+      <c r="B968" t="s">
         <v>599</v>
       </c>
-      <c r="B968" t="s">
+      <c r="C968" t="s">
         <v>600</v>
-      </c>
-      <c r="C968" t="s">
-        <v>601</v>
       </c>
       <c r="D968" t="s">
         <v>82</v>
@@ -31159,13 +31853,13 @@
     </row>
     <row r="969" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A969" t="s">
+        <v>598</v>
+      </c>
+      <c r="B969" t="s">
         <v>599</v>
       </c>
-      <c r="B969" t="s">
+      <c r="C969" t="s">
         <v>600</v>
-      </c>
-      <c r="C969" t="s">
-        <v>601</v>
       </c>
       <c r="D969" t="s">
         <v>106</v>
@@ -31174,7 +31868,7 @@
         <v>21</v>
       </c>
       <c r="F969" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G969" t="s">
         <v>43</v>
@@ -31182,13 +31876,13 @@
     </row>
     <row r="970" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A970" t="s">
+        <v>598</v>
+      </c>
+      <c r="B970" t="s">
         <v>599</v>
       </c>
-      <c r="B970" t="s">
+      <c r="C970" t="s">
         <v>600</v>
-      </c>
-      <c r="C970" t="s">
-        <v>601</v>
       </c>
       <c r="D970" t="s">
         <v>57</v>
@@ -31197,7 +31891,7 @@
         <v>21</v>
       </c>
       <c r="F970" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G970" t="s">
         <v>43</v>
@@ -31205,13 +31899,13 @@
     </row>
     <row r="971" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A971" t="s">
+        <v>598</v>
+      </c>
+      <c r="B971" t="s">
         <v>599</v>
       </c>
-      <c r="B971" t="s">
+      <c r="C971" t="s">
         <v>600</v>
-      </c>
-      <c r="C971" t="s">
-        <v>601</v>
       </c>
       <c r="D971" t="s">
         <v>82</v>
@@ -31220,7 +31914,7 @@
         <v>21</v>
       </c>
       <c r="F971" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G971" t="s">
         <v>43</v>
@@ -31228,13 +31922,13 @@
     </row>
     <row r="972" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A972" t="s">
+        <v>598</v>
+      </c>
+      <c r="B972" t="s">
         <v>599</v>
       </c>
-      <c r="B972" t="s">
+      <c r="C972" t="s">
         <v>600</v>
-      </c>
-      <c r="C972" t="s">
-        <v>601</v>
       </c>
       <c r="D972" t="s">
         <v>47</v>
@@ -31251,13 +31945,13 @@
     </row>
     <row r="973" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A973" t="s">
+        <v>598</v>
+      </c>
+      <c r="B973" t="s">
         <v>599</v>
       </c>
-      <c r="B973" t="s">
+      <c r="C973" t="s">
         <v>600</v>
-      </c>
-      <c r="C973" t="s">
-        <v>601</v>
       </c>
       <c r="D973" t="s">
         <v>47</v>
@@ -31266,7 +31960,7 @@
         <v>21</v>
       </c>
       <c r="F973" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G973" t="s">
         <v>43</v>
@@ -31274,13 +31968,13 @@
     </row>
     <row r="974" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A974" t="s">
+        <v>598</v>
+      </c>
+      <c r="B974" t="s">
         <v>599</v>
       </c>
-      <c r="B974" t="s">
+      <c r="C974" t="s">
         <v>600</v>
-      </c>
-      <c r="C974" t="s">
-        <v>601</v>
       </c>
       <c r="D974" t="s">
         <v>57</v>
@@ -31289,7 +31983,7 @@
         <v>21</v>
       </c>
       <c r="F974" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G974" t="s">
         <v>43</v>
@@ -31297,13 +31991,13 @@
     </row>
     <row r="975" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A975" t="s">
+        <v>598</v>
+      </c>
+      <c r="B975" t="s">
         <v>599</v>
       </c>
-      <c r="B975" t="s">
+      <c r="C975" t="s">
         <v>600</v>
-      </c>
-      <c r="C975" t="s">
-        <v>601</v>
       </c>
       <c r="D975" t="s">
         <v>82</v>
@@ -31312,7 +32006,7 @@
         <v>21</v>
       </c>
       <c r="F975" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G975" t="s">
         <v>43</v>
@@ -31320,13 +32014,13 @@
     </row>
     <row r="976" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A976" t="s">
+        <v>598</v>
+      </c>
+      <c r="B976" t="s">
         <v>599</v>
       </c>
-      <c r="B976" t="s">
+      <c r="C976" t="s">
         <v>600</v>
-      </c>
-      <c r="C976" t="s">
-        <v>601</v>
       </c>
       <c r="D976" t="s">
         <v>57</v>
@@ -31343,13 +32037,13 @@
     </row>
     <row r="977" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A977" t="s">
+        <v>598</v>
+      </c>
+      <c r="B977" t="s">
         <v>599</v>
       </c>
-      <c r="B977" t="s">
+      <c r="C977" t="s">
         <v>600</v>
-      </c>
-      <c r="C977" t="s">
-        <v>601</v>
       </c>
       <c r="D977" t="s">
         <v>57</v>
@@ -31366,13 +32060,13 @@
     </row>
     <row r="978" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A978" t="s">
+        <v>598</v>
+      </c>
+      <c r="B978" t="s">
         <v>599</v>
       </c>
-      <c r="B978" t="s">
+      <c r="C978" t="s">
         <v>600</v>
-      </c>
-      <c r="C978" t="s">
-        <v>601</v>
       </c>
       <c r="D978" t="s">
         <v>47</v>
@@ -31389,13 +32083,13 @@
     </row>
     <row r="979" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A979" t="s">
+        <v>598</v>
+      </c>
+      <c r="B979" t="s">
         <v>599</v>
       </c>
-      <c r="B979" t="s">
+      <c r="C979" t="s">
         <v>600</v>
-      </c>
-      <c r="C979" t="s">
-        <v>601</v>
       </c>
       <c r="D979" t="s">
         <v>115</v>
@@ -31412,13 +32106,13 @@
     </row>
     <row r="980" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A980" t="s">
+        <v>598</v>
+      </c>
+      <c r="B980" t="s">
         <v>599</v>
       </c>
-      <c r="B980" t="s">
+      <c r="C980" t="s">
         <v>600</v>
-      </c>
-      <c r="C980" t="s">
-        <v>601</v>
       </c>
       <c r="D980" t="s">
         <v>57</v>
@@ -31427,7 +32121,7 @@
         <v>21</v>
       </c>
       <c r="F980" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G980" t="s">
         <v>43</v>
@@ -31435,13 +32129,13 @@
     </row>
     <row r="981" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A981" t="s">
+        <v>598</v>
+      </c>
+      <c r="B981" t="s">
         <v>599</v>
       </c>
-      <c r="B981" t="s">
+      <c r="C981" t="s">
         <v>600</v>
-      </c>
-      <c r="C981" t="s">
-        <v>601</v>
       </c>
       <c r="D981" t="s">
         <v>57</v>
@@ -31450,7 +32144,7 @@
         <v>21</v>
       </c>
       <c r="F981" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G981" t="s">
         <v>43</v>
@@ -31458,13 +32152,13 @@
     </row>
     <row r="982" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A982" t="s">
+        <v>598</v>
+      </c>
+      <c r="B982" t="s">
         <v>599</v>
       </c>
-      <c r="B982" t="s">
+      <c r="C982" t="s">
         <v>600</v>
-      </c>
-      <c r="C982" t="s">
-        <v>601</v>
       </c>
       <c r="D982" t="s">
         <v>47</v>
@@ -31473,7 +32167,7 @@
         <v>21</v>
       </c>
       <c r="F982" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G982" t="s">
         <v>43</v>
@@ -31481,13 +32175,13 @@
     </row>
     <row r="983" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A983" t="s">
+        <v>598</v>
+      </c>
+      <c r="B983" t="s">
         <v>599</v>
       </c>
-      <c r="B983" t="s">
+      <c r="C983" t="s">
         <v>600</v>
-      </c>
-      <c r="C983" t="s">
-        <v>601</v>
       </c>
       <c r="D983" t="s">
         <v>106</v>
@@ -31496,7 +32190,7 @@
         <v>21</v>
       </c>
       <c r="F983" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G983" t="s">
         <v>43</v>
@@ -31504,13 +32198,13 @@
     </row>
     <row r="984" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A984" t="s">
+        <v>598</v>
+      </c>
+      <c r="B984" t="s">
         <v>599</v>
       </c>
-      <c r="B984" t="s">
+      <c r="C984" t="s">
         <v>600</v>
-      </c>
-      <c r="C984" t="s">
-        <v>601</v>
       </c>
       <c r="D984" t="s">
         <v>57</v>
@@ -31527,13 +32221,13 @@
     </row>
     <row r="985" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A985" t="s">
+        <v>598</v>
+      </c>
+      <c r="B985" t="s">
         <v>599</v>
       </c>
-      <c r="B985" t="s">
+      <c r="C985" t="s">
         <v>600</v>
-      </c>
-      <c r="C985" t="s">
-        <v>601</v>
       </c>
       <c r="D985" t="s">
         <v>57</v>
@@ -31550,13 +32244,13 @@
     </row>
     <row r="986" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A986" t="s">
+        <v>598</v>
+      </c>
+      <c r="B986" t="s">
         <v>599</v>
       </c>
-      <c r="B986" t="s">
+      <c r="C986" t="s">
         <v>600</v>
-      </c>
-      <c r="C986" t="s">
-        <v>601</v>
       </c>
       <c r="D986" t="s">
         <v>38</v>
@@ -31573,13 +32267,13 @@
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A987" t="s">
+        <v>598</v>
+      </c>
+      <c r="B987" t="s">
         <v>599</v>
       </c>
-      <c r="B987" t="s">
+      <c r="C987" t="s">
         <v>600</v>
-      </c>
-      <c r="C987" t="s">
-        <v>601</v>
       </c>
       <c r="D987" t="s">
         <v>57</v>
@@ -31596,13 +32290,13 @@
     </row>
     <row r="988" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A988" t="s">
+        <v>598</v>
+      </c>
+      <c r="B988" t="s">
         <v>599</v>
       </c>
-      <c r="B988" t="s">
+      <c r="C988" t="s">
         <v>600</v>
-      </c>
-      <c r="C988" t="s">
-        <v>601</v>
       </c>
       <c r="D988" t="s">
         <v>57</v>
@@ -31619,13 +32313,13 @@
     </row>
     <row r="989" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A989" t="s">
+        <v>598</v>
+      </c>
+      <c r="B989" t="s">
         <v>599</v>
       </c>
-      <c r="B989" t="s">
+      <c r="C989" t="s">
         <v>600</v>
-      </c>
-      <c r="C989" t="s">
-        <v>601</v>
       </c>
       <c r="D989" t="s">
         <v>106</v>
@@ -31634,7 +32328,7 @@
         <v>21</v>
       </c>
       <c r="F989" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G989" t="s">
         <v>43</v>
@@ -31642,13 +32336,13 @@
     </row>
     <row r="990" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A990" t="s">
+        <v>598</v>
+      </c>
+      <c r="B990" t="s">
         <v>599</v>
       </c>
-      <c r="B990" t="s">
+      <c r="C990" t="s">
         <v>600</v>
-      </c>
-      <c r="C990" t="s">
-        <v>601</v>
       </c>
       <c r="D990" t="s">
         <v>57</v>
@@ -31657,7 +32351,7 @@
         <v>21</v>
       </c>
       <c r="F990" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G990" t="s">
         <v>43</v>
@@ -31665,13 +32359,13 @@
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A991" t="s">
+        <v>598</v>
+      </c>
+      <c r="B991" t="s">
         <v>599</v>
       </c>
-      <c r="B991" t="s">
+      <c r="C991" t="s">
         <v>600</v>
-      </c>
-      <c r="C991" t="s">
-        <v>601</v>
       </c>
       <c r="D991" t="s">
         <v>57</v>
@@ -31680,7 +32374,7 @@
         <v>21</v>
       </c>
       <c r="F991" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G991" t="s">
         <v>43</v>
@@ -31688,13 +32382,13 @@
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A992" t="s">
+        <v>598</v>
+      </c>
+      <c r="B992" t="s">
         <v>599</v>
       </c>
-      <c r="B992" t="s">
+      <c r="C992" t="s">
         <v>600</v>
-      </c>
-      <c r="C992" t="s">
-        <v>601</v>
       </c>
       <c r="D992" t="s">
         <v>57</v>
@@ -31711,13 +32405,13 @@
     </row>
     <row r="993" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A993" t="s">
+        <v>598</v>
+      </c>
+      <c r="B993" t="s">
         <v>599</v>
       </c>
-      <c r="B993" t="s">
+      <c r="C993" t="s">
         <v>600</v>
-      </c>
-      <c r="C993" t="s">
-        <v>601</v>
       </c>
       <c r="D993" t="s">
         <v>82</v>
@@ -31737,10 +32431,10 @@
         <v>576</v>
       </c>
       <c r="B994" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C994" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D994" t="s">
         <v>357</v>
@@ -31749,7 +32443,7 @@
         <v>532</v>
       </c>
       <c r="F994" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G994" t="s">
         <v>68</v>
@@ -31757,10 +32451,10 @@
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A995" t="s">
+        <v>610</v>
+      </c>
+      <c r="B995" t="s">
         <v>611</v>
-      </c>
-      <c r="B995" t="s">
-        <v>612</v>
       </c>
       <c r="C995" t="s">
         <v>213</v>
@@ -31769,10 +32463,10 @@
         <v>77</v>
       </c>
       <c r="E995" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F995" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G995" t="s">
         <v>43</v>
@@ -31780,10 +32474,10 @@
     </row>
     <row r="996" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A996" t="s">
+        <v>610</v>
+      </c>
+      <c r="B996" t="s">
         <v>611</v>
-      </c>
-      <c r="B996" t="s">
-        <v>612</v>
       </c>
       <c r="C996" t="s">
         <v>213</v>
@@ -31803,19 +32497,19 @@
     </row>
     <row r="997" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A997" t="s">
+        <v>610</v>
+      </c>
+      <c r="B997" t="s">
         <v>611</v>
-      </c>
-      <c r="B997" t="s">
-        <v>612</v>
       </c>
       <c r="C997" t="s">
         <v>213</v>
       </c>
       <c r="D997" t="s">
+        <v>613</v>
+      </c>
+      <c r="E997" t="s">
         <v>614</v>
-      </c>
-      <c r="E997" t="s">
-        <v>615</v>
       </c>
       <c r="F997" t="s">
         <v>145</v>
@@ -31826,10 +32520,10 @@
     </row>
     <row r="998" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A998" t="s">
+        <v>610</v>
+      </c>
+      <c r="B998" t="s">
         <v>611</v>
-      </c>
-      <c r="B998" t="s">
-        <v>612</v>
       </c>
       <c r="C998" t="s">
         <v>213</v>
@@ -31849,10 +32543,10 @@
     </row>
     <row r="999" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A999" t="s">
+        <v>610</v>
+      </c>
+      <c r="B999" t="s">
         <v>611</v>
-      </c>
-      <c r="B999" t="s">
-        <v>612</v>
       </c>
       <c r="C999" t="s">
         <v>213</v>
@@ -31872,10 +32566,10 @@
     </row>
     <row r="1000" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1000" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1000" t="s">
         <v>611</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>612</v>
       </c>
       <c r="C1000" t="s">
         <v>213</v>
@@ -31895,10 +32589,10 @@
     </row>
     <row r="1001" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1001" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1001" t="s">
         <v>611</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>612</v>
       </c>
       <c r="C1001" t="s">
         <v>213</v>
@@ -31918,10 +32612,10 @@
     </row>
     <row r="1002" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1002" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1002" t="s">
         <v>611</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>612</v>
       </c>
       <c r="C1002" t="s">
         <v>213</v>
@@ -31930,7 +32624,7 @@
         <v>38</v>
       </c>
       <c r="E1002" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F1002" t="s">
         <v>145</v>
@@ -31944,22 +32638,22 @@
         <v>577</v>
       </c>
       <c r="B1003" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C1003" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D1003" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E1003" t="s">
         <v>129</v>
       </c>
       <c r="F1003" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G1003" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1004" spans="1:7" x14ac:dyDescent="0.2">
@@ -31967,19 +32661,19 @@
         <v>578</v>
       </c>
       <c r="B1004" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1004" t="s">
         <v>632</v>
-      </c>
-      <c r="C1004" t="s">
-        <v>633</v>
       </c>
       <c r="D1004" t="s">
         <v>54</v>
       </c>
       <c r="E1004" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F1004" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G1004" t="s">
         <v>43</v>
@@ -31990,10 +32684,10 @@
         <v>578</v>
       </c>
       <c r="B1005" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1005" t="s">
         <v>632</v>
-      </c>
-      <c r="C1005" t="s">
-        <v>633</v>
       </c>
       <c r="D1005" t="s">
         <v>54</v>
@@ -32002,7 +32696,7 @@
         <v>65</v>
       </c>
       <c r="F1005" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G1005" t="s">
         <v>43</v>
@@ -32013,10 +32707,10 @@
         <v>578</v>
       </c>
       <c r="B1006" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1006" t="s">
         <v>632</v>
-      </c>
-      <c r="C1006" t="s">
-        <v>633</v>
       </c>
       <c r="D1006" t="s">
         <v>54</v>
@@ -32025,7 +32719,7 @@
         <v>65</v>
       </c>
       <c r="F1006" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G1006" t="s">
         <v>43</v>
@@ -32036,19 +32730,19 @@
         <v>578</v>
       </c>
       <c r="B1007" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1007" t="s">
         <v>632</v>
-      </c>
-      <c r="C1007" t="s">
-        <v>633</v>
       </c>
       <c r="D1007" t="s">
         <v>127</v>
       </c>
       <c r="E1007" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F1007" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G1007" t="s">
         <v>43</v>
@@ -32059,10 +32753,10 @@
         <v>578</v>
       </c>
       <c r="B1008" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1008" t="s">
         <v>632</v>
-      </c>
-      <c r="C1008" t="s">
-        <v>633</v>
       </c>
       <c r="D1008" t="s">
         <v>62</v>
@@ -32082,19 +32776,19 @@
         <v>578</v>
       </c>
       <c r="B1009" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1009" t="s">
         <v>632</v>
-      </c>
-      <c r="C1009" t="s">
-        <v>633</v>
       </c>
       <c r="D1009" t="s">
         <v>172</v>
       </c>
       <c r="E1009" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F1009" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G1009" t="s">
         <v>43</v>
@@ -32105,19 +32799,19 @@
         <v>578</v>
       </c>
       <c r="B1010" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1010" t="s">
         <v>632</v>
-      </c>
-      <c r="C1010" t="s">
-        <v>633</v>
       </c>
       <c r="D1010" t="s">
         <v>522</v>
       </c>
       <c r="E1010" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F1010" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G1010" t="s">
         <v>43</v>
@@ -32128,19 +32822,19 @@
         <v>578</v>
       </c>
       <c r="B1011" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1011" t="s">
         <v>632</v>
-      </c>
-      <c r="C1011" t="s">
-        <v>633</v>
       </c>
       <c r="D1011" t="s">
         <v>51</v>
       </c>
       <c r="E1011" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F1011" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G1011" t="s">
         <v>43</v>
@@ -32151,16 +32845,16 @@
         <v>578</v>
       </c>
       <c r="B1012" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1012" t="s">
         <v>632</v>
-      </c>
-      <c r="C1012" t="s">
-        <v>633</v>
       </c>
       <c r="D1012" t="s">
         <v>345</v>
       </c>
       <c r="E1012" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F1012" t="s">
         <v>105</v>
@@ -32174,16 +32868,16 @@
         <v>578</v>
       </c>
       <c r="B1013" t="s">
+        <v>631</v>
+      </c>
+      <c r="C1013" t="s">
         <v>632</v>
-      </c>
-      <c r="C1013" t="s">
-        <v>633</v>
       </c>
       <c r="D1013" t="s">
         <v>345</v>
       </c>
       <c r="E1013" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F1013" t="s">
         <v>105</v>
@@ -32197,7 +32891,7 @@
         <v>579</v>
       </c>
       <c r="B1014" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C1014" t="s">
         <v>151</v>
@@ -32206,10 +32900,10 @@
         <v>114</v>
       </c>
       <c r="E1014" t="s">
+        <v>634</v>
+      </c>
+      <c r="F1014" t="s">
         <v>635</v>
-      </c>
-      <c r="F1014" t="s">
-        <v>636</v>
       </c>
       <c r="G1014" t="s">
         <v>68</v>
@@ -32220,7 +32914,7 @@
         <v>579</v>
       </c>
       <c r="B1015" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C1015" t="s">
         <v>151</v>
@@ -32232,7 +32926,7 @@
         <v>21</v>
       </c>
       <c r="F1015" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G1015" t="s">
         <v>68</v>
@@ -32243,19 +32937,19 @@
         <v>580</v>
       </c>
       <c r="B1016" t="s">
+        <v>636</v>
+      </c>
+      <c r="C1016" t="s">
+        <v>678</v>
+      </c>
+      <c r="D1016" t="s">
+        <v>638</v>
+      </c>
+      <c r="E1016" t="s">
+        <v>639</v>
+      </c>
+      <c r="F1016" t="s">
         <v>637</v>
-      </c>
-      <c r="C1016" t="s">
-        <v>679</v>
-      </c>
-      <c r="D1016" t="s">
-        <v>639</v>
-      </c>
-      <c r="E1016" t="s">
-        <v>640</v>
-      </c>
-      <c r="F1016" t="s">
-        <v>638</v>
       </c>
       <c r="G1016" t="s">
         <v>68</v>
@@ -32266,10 +32960,10 @@
         <v>581</v>
       </c>
       <c r="B1017" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C1017" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D1017" t="s">
         <v>86</v>
@@ -32278,10 +32972,10 @@
         <v>21</v>
       </c>
       <c r="F1017" t="s">
+        <v>641</v>
+      </c>
+      <c r="G1017" t="s">
         <v>642</v>
-      </c>
-      <c r="G1017" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="1018" spans="1:7" x14ac:dyDescent="0.2">
@@ -32289,10 +32983,10 @@
         <v>582</v>
       </c>
       <c r="B1018" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C1018" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D1018" t="s">
         <v>57</v>
@@ -32304,7 +32998,7 @@
         <v>146</v>
       </c>
       <c r="G1018" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1019" spans="1:7" x14ac:dyDescent="0.2">
@@ -32312,10 +33006,10 @@
         <v>582</v>
       </c>
       <c r="B1019" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C1019" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D1019" t="s">
         <v>79</v>
@@ -32327,7 +33021,7 @@
         <v>146</v>
       </c>
       <c r="G1019" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1020" spans="1:7" x14ac:dyDescent="0.2">
@@ -32335,10 +33029,10 @@
         <v>582</v>
       </c>
       <c r="B1020" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C1020" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D1020" t="s">
         <v>81</v>
@@ -32350,7 +33044,7 @@
         <v>146</v>
       </c>
       <c r="G1020" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.2">
@@ -32358,19 +33052,19 @@
         <v>583</v>
       </c>
       <c r="B1021" t="s">
+        <v>650</v>
+      </c>
+      <c r="C1021" t="s">
         <v>651</v>
       </c>
-      <c r="C1021" t="s">
+      <c r="D1021" t="s">
+        <v>613</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>645</v>
+      </c>
+      <c r="F1021" t="s">
         <v>652</v>
-      </c>
-      <c r="D1021" t="s">
-        <v>614</v>
-      </c>
-      <c r="E1021" t="s">
-        <v>646</v>
-      </c>
-      <c r="F1021" t="s">
-        <v>653</v>
       </c>
       <c r="G1021" t="s">
         <v>43</v>
@@ -32381,19 +33075,19 @@
         <v>583</v>
       </c>
       <c r="B1022" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C1022" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D1022" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1022" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F1022" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G1022" t="s">
         <v>43</v>
@@ -32404,16 +33098,16 @@
         <v>583</v>
       </c>
       <c r="B1023" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C1023" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D1023" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1023" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F1023" t="s">
         <v>240</v>
@@ -32427,16 +33121,16 @@
         <v>583</v>
       </c>
       <c r="B1024" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C1024" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D1024" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1024" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F1024" t="s">
         <v>240</v>
@@ -32450,16 +33144,16 @@
         <v>583</v>
       </c>
       <c r="B1025" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C1025" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D1025" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1025" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F1025" t="s">
         <v>240</v>
@@ -32470,19 +33164,19 @@
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1026" t="s">
+        <v>654</v>
+      </c>
+      <c r="B1026" t="s">
         <v>655</v>
       </c>
-      <c r="B1026" t="s">
-        <v>656</v>
-      </c>
       <c r="C1026" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D1026" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1026" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F1026" t="s">
         <v>240</v>
@@ -32493,22 +33187,22 @@
     </row>
     <row r="1027" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1027" t="s">
+        <v>654</v>
+      </c>
+      <c r="B1027" t="s">
         <v>655</v>
       </c>
-      <c r="B1027" t="s">
+      <c r="C1027" t="s">
+        <v>673</v>
+      </c>
+      <c r="D1027" t="s">
+        <v>613</v>
+      </c>
+      <c r="E1027" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1027" t="s">
         <v>656</v>
-      </c>
-      <c r="C1027" t="s">
-        <v>674</v>
-      </c>
-      <c r="D1027" t="s">
-        <v>614</v>
-      </c>
-      <c r="E1027" t="s">
-        <v>615</v>
-      </c>
-      <c r="F1027" t="s">
-        <v>657</v>
       </c>
       <c r="G1027" t="s">
         <v>43</v>
@@ -32516,16 +33210,16 @@
     </row>
     <row r="1028" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1028" t="s">
+        <v>654</v>
+      </c>
+      <c r="B1028" t="s">
         <v>655</v>
       </c>
-      <c r="B1028" t="s">
-        <v>656</v>
-      </c>
       <c r="C1028" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D1028" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E1028" t="s">
         <v>21</v>
@@ -32539,22 +33233,22 @@
     </row>
     <row r="1029" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1029" t="s">
+        <v>654</v>
+      </c>
+      <c r="B1029" t="s">
         <v>655</v>
       </c>
-      <c r="B1029" t="s">
-        <v>656</v>
-      </c>
       <c r="C1029" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D1029" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E1029" t="s">
         <v>21</v>
       </c>
       <c r="F1029" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G1029" t="s">
         <v>43</v>
@@ -32562,19 +33256,19 @@
     </row>
     <row r="1030" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1030" t="s">
+        <v>662</v>
+      </c>
+      <c r="B1030" t="s">
         <v>663</v>
       </c>
-      <c r="B1030" t="s">
+      <c r="C1030" t="s">
         <v>664</v>
       </c>
-      <c r="C1030" t="s">
-        <v>665</v>
-      </c>
       <c r="D1030" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1030" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F1030" t="s">
         <v>240</v>
@@ -32585,19 +33279,19 @@
     </row>
     <row r="1031" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1031" t="s">
+        <v>662</v>
+      </c>
+      <c r="B1031" t="s">
         <v>663</v>
       </c>
-      <c r="B1031" t="s">
-        <v>664</v>
-      </c>
       <c r="C1031" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D1031" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1031" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F1031" t="s">
         <v>240</v>
@@ -32608,19 +33302,19 @@
     </row>
     <row r="1032" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1032" t="s">
+        <v>662</v>
+      </c>
+      <c r="B1032" t="s">
         <v>663</v>
       </c>
-      <c r="B1032" t="s">
-        <v>664</v>
-      </c>
       <c r="C1032" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D1032" t="s">
+        <v>613</v>
+      </c>
+      <c r="E1032" t="s">
         <v>614</v>
-      </c>
-      <c r="E1032" t="s">
-        <v>615</v>
       </c>
       <c r="F1032" t="s">
         <v>101</v>
@@ -32631,19 +33325,19 @@
     </row>
     <row r="1033" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1033" t="s">
+        <v>662</v>
+      </c>
+      <c r="B1033" t="s">
         <v>663</v>
       </c>
-      <c r="B1033" t="s">
-        <v>664</v>
-      </c>
       <c r="C1033" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D1033" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1033" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F1033" t="s">
         <v>240</v>
@@ -32657,22 +33351,22 @@
         <v>584</v>
       </c>
       <c r="B1034" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1034" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D1034" t="s">
         <v>77</v>
       </c>
       <c r="E1034" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F1034" t="s">
         <v>101</v>
       </c>
       <c r="G1034" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1035" spans="1:7" x14ac:dyDescent="0.2">
@@ -32680,10 +33374,10 @@
         <v>584</v>
       </c>
       <c r="B1035" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1035" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D1035" t="s">
         <v>53</v>
@@ -32692,10 +33386,10 @@
         <v>464</v>
       </c>
       <c r="F1035" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G1035" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1036" spans="1:7" x14ac:dyDescent="0.2">
@@ -32703,22 +33397,22 @@
         <v>584</v>
       </c>
       <c r="B1036" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1036" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D1036" t="s">
+        <v>701</v>
+      </c>
+      <c r="E1036" t="s">
         <v>702</v>
       </c>
-      <c r="E1036" t="s">
-        <v>703</v>
-      </c>
       <c r="F1036" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G1036" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1037" spans="1:7" x14ac:dyDescent="0.2">
@@ -32726,22 +33420,22 @@
         <v>584</v>
       </c>
       <c r="B1037" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1037" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D1037" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E1037" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F1037" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G1037" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1038" spans="1:7" x14ac:dyDescent="0.2">
@@ -32749,13 +33443,13 @@
         <v>584</v>
       </c>
       <c r="B1038" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1038" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D1038" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E1038" t="s">
         <v>84</v>
@@ -32764,7 +33458,7 @@
         <v>101</v>
       </c>
       <c r="G1038" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1039" spans="1:7" x14ac:dyDescent="0.2">
@@ -32772,7 +33466,7 @@
         <v>584</v>
       </c>
       <c r="B1039" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1039" t="s">
         <v>142</v>
@@ -32787,7 +33481,7 @@
         <v>16</v>
       </c>
       <c r="G1039" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1040" spans="1:7" x14ac:dyDescent="0.2">
@@ -32795,7 +33489,7 @@
         <v>584</v>
       </c>
       <c r="B1040" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1040" t="s">
         <v>142</v>
@@ -32804,13 +33498,13 @@
         <v>70</v>
       </c>
       <c r="E1040" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F1040" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G1040" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1041" spans="1:7" x14ac:dyDescent="0.2">
@@ -32818,10 +33512,10 @@
         <v>584</v>
       </c>
       <c r="B1041" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1041" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D1041" t="s">
         <v>54</v>
@@ -32833,7 +33527,7 @@
         <v>101</v>
       </c>
       <c r="G1041" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1042" spans="1:7" x14ac:dyDescent="0.2">
@@ -32841,10 +33535,10 @@
         <v>584</v>
       </c>
       <c r="B1042" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1042" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D1042" t="s">
         <v>54</v>
@@ -32856,7 +33550,7 @@
         <v>429</v>
       </c>
       <c r="G1042" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1043" spans="1:7" x14ac:dyDescent="0.2">
@@ -32864,10 +33558,10 @@
         <v>584</v>
       </c>
       <c r="B1043" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1043" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D1043" t="s">
         <v>54</v>
@@ -32879,7 +33573,7 @@
         <v>429</v>
       </c>
       <c r="G1043" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1044" spans="1:7" x14ac:dyDescent="0.2">
@@ -32887,10 +33581,10 @@
         <v>584</v>
       </c>
       <c r="B1044" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1044" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D1044" t="s">
         <v>30</v>
@@ -32902,7 +33596,7 @@
         <v>16</v>
       </c>
       <c r="G1044" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1045" spans="1:7" x14ac:dyDescent="0.2">
@@ -32910,10 +33604,10 @@
         <v>584</v>
       </c>
       <c r="B1045" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1045" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D1045" t="s">
         <v>82</v>
@@ -32925,7 +33619,7 @@
         <v>16</v>
       </c>
       <c r="G1045" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1046" spans="1:7" x14ac:dyDescent="0.2">
@@ -32933,22 +33627,22 @@
         <v>584</v>
       </c>
       <c r="B1046" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1046" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D1046" t="s">
         <v>568</v>
       </c>
       <c r="E1046" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F1046" t="s">
         <v>101</v>
       </c>
       <c r="G1046" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1047" spans="1:7" x14ac:dyDescent="0.2">
@@ -32956,10 +33650,10 @@
         <v>584</v>
       </c>
       <c r="B1047" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1047" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D1047" t="s">
         <v>123</v>
@@ -32971,7 +33665,7 @@
         <v>136</v>
       </c>
       <c r="G1047" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1048" spans="1:7" x14ac:dyDescent="0.2">
@@ -32979,10 +33673,10 @@
         <v>584</v>
       </c>
       <c r="B1048" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1048" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D1048" t="s">
         <v>437</v>
@@ -32994,7 +33688,7 @@
         <v>16</v>
       </c>
       <c r="G1048" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1049" spans="1:7" x14ac:dyDescent="0.2">
@@ -33002,22 +33696,22 @@
         <v>584</v>
       </c>
       <c r="B1049" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1049" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D1049" t="s">
         <v>127</v>
       </c>
       <c r="E1049" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F1049" t="s">
         <v>101</v>
       </c>
       <c r="G1049" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1050" spans="1:7" x14ac:dyDescent="0.2">
@@ -33025,10 +33719,10 @@
         <v>584</v>
       </c>
       <c r="B1050" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1050" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D1050" t="s">
         <v>401</v>
@@ -33040,7 +33734,7 @@
         <v>396</v>
       </c>
       <c r="G1050" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1051" spans="1:7" x14ac:dyDescent="0.2">
@@ -33048,10 +33742,10 @@
         <v>584</v>
       </c>
       <c r="B1051" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1051" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D1051" t="s">
         <v>88</v>
@@ -33063,7 +33757,7 @@
         <v>101</v>
       </c>
       <c r="G1051" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1052" spans="1:7" x14ac:dyDescent="0.2">
@@ -33071,10 +33765,10 @@
         <v>584</v>
       </c>
       <c r="B1052" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1052" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D1052" t="s">
         <v>51</v>
@@ -33083,10 +33777,10 @@
         <v>93</v>
       </c>
       <c r="F1052" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G1052" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1053" spans="1:7" x14ac:dyDescent="0.2">
@@ -33094,7 +33788,7 @@
         <v>584</v>
       </c>
       <c r="B1053" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1053" t="s">
         <v>146</v>
@@ -33106,10 +33800,10 @@
         <v>149</v>
       </c>
       <c r="F1053" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G1053" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1054" spans="1:7" x14ac:dyDescent="0.2">
@@ -33117,7 +33811,7 @@
         <v>584</v>
       </c>
       <c r="B1054" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1054" t="s">
         <v>142</v>
@@ -33129,10 +33823,10 @@
         <v>131</v>
       </c>
       <c r="F1054" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G1054" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1055" spans="1:7" x14ac:dyDescent="0.2">
@@ -33140,7 +33834,7 @@
         <v>584</v>
       </c>
       <c r="B1055" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1055" t="s">
         <v>164</v>
@@ -33155,7 +33849,7 @@
         <v>105</v>
       </c>
       <c r="G1055" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1056" spans="1:7" x14ac:dyDescent="0.2">
@@ -33163,10 +33857,10 @@
         <v>584</v>
       </c>
       <c r="B1056" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1056" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D1056" t="s">
         <v>51</v>
@@ -33175,10 +33869,10 @@
         <v>409</v>
       </c>
       <c r="F1056" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G1056" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1057" spans="1:7" x14ac:dyDescent="0.2">
@@ -33186,10 +33880,10 @@
         <v>584</v>
       </c>
       <c r="B1057" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1057" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D1057" t="s">
         <v>95</v>
@@ -33198,10 +33892,10 @@
         <v>96</v>
       </c>
       <c r="F1057" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G1057" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1058" spans="1:7" x14ac:dyDescent="0.2">
@@ -33209,22 +33903,22 @@
         <v>584</v>
       </c>
       <c r="B1058" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1058" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D1058" t="s">
         <v>441</v>
       </c>
       <c r="E1058" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F1058" t="s">
         <v>101</v>
       </c>
       <c r="G1058" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1059" spans="1:7" x14ac:dyDescent="0.2">
@@ -33232,7 +33926,7 @@
         <v>584</v>
       </c>
       <c r="B1059" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1059" t="s">
         <v>146</v>
@@ -33241,13 +33935,13 @@
         <v>441</v>
       </c>
       <c r="E1059" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F1059" t="s">
         <v>101</v>
       </c>
       <c r="G1059" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1060" spans="1:7" x14ac:dyDescent="0.2">
@@ -33255,22 +33949,22 @@
         <v>584</v>
       </c>
       <c r="B1060" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1060" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D1060" t="s">
         <v>441</v>
       </c>
       <c r="E1060" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F1060" t="s">
         <v>101</v>
       </c>
       <c r="G1060" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1061" spans="1:7" x14ac:dyDescent="0.2">
@@ -33278,22 +33972,22 @@
         <v>584</v>
       </c>
       <c r="B1061" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1061" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D1061" t="s">
         <v>441</v>
       </c>
       <c r="E1061" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F1061" t="s">
         <v>101</v>
       </c>
       <c r="G1061" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1062" spans="1:7" x14ac:dyDescent="0.2">
@@ -33301,7 +33995,7 @@
         <v>584</v>
       </c>
       <c r="B1062" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1062" t="s">
         <v>168</v>
@@ -33313,10 +34007,10 @@
         <v>63</v>
       </c>
       <c r="F1062" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G1062" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1063" spans="1:7" x14ac:dyDescent="0.2">
@@ -33324,7 +34018,7 @@
         <v>584</v>
       </c>
       <c r="B1063" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1063" t="s">
         <v>146</v>
@@ -33339,7 +34033,7 @@
         <v>101</v>
       </c>
       <c r="G1063" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1064" spans="1:7" x14ac:dyDescent="0.2">
@@ -33347,10 +34041,10 @@
         <v>584</v>
       </c>
       <c r="B1064" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C1064" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D1064" t="s">
         <v>62</v>
@@ -33359,21 +34053,21 @@
         <v>100</v>
       </c>
       <c r="F1064" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G1064" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="1065" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1065" t="s">
-        <v>585</v>
+        <v>817</v>
       </c>
       <c r="B1065" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C1065" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D1065" t="s">
         <v>38</v>
@@ -33382,24 +34076,24 @@
         <v>361</v>
       </c>
       <c r="F1065" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G1065" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="1066" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1066" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B1066" t="s">
+        <v>718</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1066" t="s">
         <v>719</v>
-      </c>
-      <c r="C1066" t="s">
-        <v>721</v>
-      </c>
-      <c r="D1066" t="s">
-        <v>720</v>
       </c>
       <c r="E1066" t="s">
         <v>21</v>
@@ -33408,18 +34102,18 @@
         <v>101</v>
       </c>
       <c r="G1066" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1067" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1067" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B1067" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1067" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D1067" t="s">
         <v>76</v>
@@ -33428,18 +34122,18 @@
         <v>21</v>
       </c>
       <c r="F1067" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G1067" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1068" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1068" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B1068" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1068" t="s">
         <v>557</v>
@@ -33454,18 +34148,18 @@
         <v>101</v>
       </c>
       <c r="G1068" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1069" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1069" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B1069" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1069" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D1069" t="s">
         <v>47</v>
@@ -33477,18 +34171,18 @@
         <v>101</v>
       </c>
       <c r="G1069" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1070" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B1070" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1070" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D1070" t="s">
         <v>47</v>
@@ -33497,21 +34191,21 @@
         <v>21</v>
       </c>
       <c r="F1070" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G1070" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1071" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1071" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B1071" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1071" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D1071" t="s">
         <v>82</v>
@@ -33523,41 +34217,41 @@
         <v>101</v>
       </c>
       <c r="G1071" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1072" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B1072" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C1072" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D1072" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E1072" t="s">
         <v>21</v>
       </c>
       <c r="F1072" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G1072" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="1073" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1073" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1073" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C1073" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D1073" t="s">
         <v>132</v>
@@ -33574,59 +34268,59 @@
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1074" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B1074" t="s">
+        <v>732</v>
+      </c>
+      <c r="C1074" t="s">
+        <v>735</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>730</v>
+      </c>
+      <c r="E1074" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1074" t="s">
+        <v>734</v>
+      </c>
+      <c r="G1074" t="s">
         <v>733</v>
-      </c>
-      <c r="C1074" t="s">
-        <v>736</v>
-      </c>
-      <c r="D1074" t="s">
-        <v>731</v>
-      </c>
-      <c r="E1074" t="s">
-        <v>732</v>
-      </c>
-      <c r="F1074" t="s">
-        <v>735</v>
-      </c>
-      <c r="G1074" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1075" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1075" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1075" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1075" t="s">
         <v>57</v>
       </c>
       <c r="E1075" t="s">
+        <v>739</v>
+      </c>
+      <c r="F1075" t="s">
         <v>740</v>
       </c>
-      <c r="F1075" t="s">
-        <v>741</v>
-      </c>
       <c r="G1075" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1076" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1076" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1076" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1076" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1076" t="s">
         <v>57</v>
@@ -33635,21 +34329,21 @@
         <v>21</v>
       </c>
       <c r="F1076" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G1076" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1077" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1077" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1077" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1077" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1077" t="s">
         <v>57</v>
@@ -33658,21 +34352,21 @@
         <v>374</v>
       </c>
       <c r="F1077" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G1077" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1078" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1078" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1078" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1078" t="s">
         <v>57</v>
@@ -33681,21 +34375,21 @@
         <v>21</v>
       </c>
       <c r="F1078" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G1078" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1079" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1079" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1079" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1079" t="s">
         <v>57</v>
@@ -33704,21 +34398,21 @@
         <v>21</v>
       </c>
       <c r="F1079" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G1079" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1080" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1080" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1080" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1080" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1080" t="s">
         <v>57</v>
@@ -33727,44 +34421,44 @@
         <v>495</v>
       </c>
       <c r="F1080" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G1080" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1081" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1081" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1081" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1081" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1081" t="s">
         <v>57</v>
       </c>
       <c r="E1081" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F1081" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G1081" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1082" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1082" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1082" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1082" t="s">
         <v>57</v>
@@ -33773,44 +34467,44 @@
         <v>472</v>
       </c>
       <c r="F1082" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G1082" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1083" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1083" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1083" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1083" t="s">
         <v>57</v>
       </c>
       <c r="E1083" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F1083" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G1083" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1084" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1084" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1084" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1084" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1084" t="s">
         <v>508</v>
@@ -33819,64 +34513,64 @@
         <v>119</v>
       </c>
       <c r="F1084" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G1084" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1085" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1085" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1085" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1085" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1085" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E1085" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F1085" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G1085" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1086" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1086" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B1086" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C1086" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D1086" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E1086" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F1086" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G1086" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1087" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B1087" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C1087" t="s">
         <v>168</v>
@@ -33888,7 +34582,7 @@
         <v>63</v>
       </c>
       <c r="F1087" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G1087" t="s">
         <v>221</v>
@@ -33896,13 +34590,13 @@
     </row>
     <row r="1088" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1088" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B1088" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C1088" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D1088" t="s">
         <v>79</v>
@@ -33919,13 +34613,13 @@
     </row>
     <row r="1089" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1089" t="s">
+        <v>753</v>
+      </c>
+      <c r="B1089" t="s">
         <v>754</v>
       </c>
-      <c r="B1089" t="s">
-        <v>755</v>
-      </c>
       <c r="C1089" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D1089" t="s">
         <v>79</v>
@@ -33934,10 +34628,4035 @@
         <v>317</v>
       </c>
       <c r="F1089" t="s">
+        <v>755</v>
+      </c>
+      <c r="G1089" t="s">
         <v>756</v>
       </c>
-      <c r="G1089" t="s">
+    </row>
+    <row r="1090" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1090" t="s">
+        <v>758</v>
+      </c>
+      <c r="B1090" t="s">
+        <v>759</v>
+      </c>
+      <c r="C1090" t="s">
+        <v>665</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1090" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1090" t="s">
         <v>757</v>
+      </c>
+      <c r="G1090" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1091" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1091" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1091" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1091" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1091" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1091" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1092" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1092" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1092" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1092" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1092" t="s">
+        <v>622</v>
+      </c>
+      <c r="F1092" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1092" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1093" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1093" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1093" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1093" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1093" t="s">
+        <v>622</v>
+      </c>
+      <c r="F1093" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1093" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1094" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1094" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1094" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1094" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1094" t="s">
+        <v>622</v>
+      </c>
+      <c r="F1094" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1094" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1095" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1095" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1095" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1095" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1095" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1095" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1096" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1096" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1096" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1096" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1096" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1097" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1097" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1097" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1097" t="s">
+        <v>622</v>
+      </c>
+      <c r="F1097" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1097" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1098" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1098" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1098" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1098" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1098" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1098" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1099" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1099" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1099" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1099" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1099" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1099" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1100" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1100" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1100" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1100" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1100" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1100" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1101" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1101" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1101" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1101" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1101" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1101" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1102" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1102" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1102" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1102" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1102" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1103" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1103" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1103" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1103" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1103" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1104" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1104" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1104" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1104" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1104" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1105" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1105" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1105" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1105" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1105" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1105" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1105" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1106" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1106" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1106" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1106" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1106" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1106" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1106" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1107" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1107" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1107" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1107" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1107" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1107" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1107" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1108" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1108" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1108" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1108" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1108" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1108" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1108" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1109" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1109" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1109" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1109" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1109" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1109" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1109" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1110" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1110" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1110" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1110" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1110" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1110" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1110" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1111" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1111" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1111" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1111" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1111" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1111" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1111" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1112" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1112" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1112" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1112" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1112" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1112" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1113" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1113" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1113" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1113" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1113" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1113" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1113" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1114" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1114" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1114" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1114" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1114" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1114" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1114" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1115" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1115" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1115" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1115" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1115" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1115" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1115" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1116" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1116" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1116" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1116" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1116" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1116" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1116" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1117" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1117" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1117" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1117" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1117" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1117" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1117" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1118" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1118" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1118" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1118" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1118" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1118" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1119" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1119" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1119" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1119" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1119" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1119" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1119" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1120" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1120" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1120" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1120" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1120" t="s">
+        <v>770</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1120" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1121" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1121" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1121" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1121" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1121" t="s">
+        <v>770</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1121" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1122" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1122" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1122" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1122" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1122" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1122" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1123" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1123" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1123" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1123" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1123" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1123" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1123" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1124" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1124" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1124" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1124" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1124" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1124" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1125" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1125" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1125" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1125" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1125" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1125" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1126" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1126" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1126" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1126" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1126" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1126" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1126" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1127" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1127" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1127" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1127" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1127" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1127" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1127" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1128" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1128" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1128" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1128" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1128" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1128" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1128" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1129" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1129" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1129" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1129" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1129" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1129" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1129" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1130" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1130" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1130" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1130" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1130" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1130" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1130" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1131" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1131" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1131" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1131" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1131" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1131" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1131" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1132" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1132" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1132" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1132" t="s">
+        <v>522</v>
+      </c>
+      <c r="E1132" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1132" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1132" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1133" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1133" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1133" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1133" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1133" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1133" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1133" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1134" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1134" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1134" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1134" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1134" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1134" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1134" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1135" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1135" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1135" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1135" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1135" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1135" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1135" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1136" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1136" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1136" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1136" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1136" t="s">
+        <v>935</v>
+      </c>
+      <c r="F1136" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1136" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1137" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1137" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1137" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1137" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1137" t="s">
+        <v>405</v>
+      </c>
+      <c r="F1137" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1137" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1138" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1138" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1138" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1138" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1138" t="s">
+        <v>405</v>
+      </c>
+      <c r="F1138" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1138" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1139" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1139" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1139" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1139" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1139" t="s">
+        <v>405</v>
+      </c>
+      <c r="F1139" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1139" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1140" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1140" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1140" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1140" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1140" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1140" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1140" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1141" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1141" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1141" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1141" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1141" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1141" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1141" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1142" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1142" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1142" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1142" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1142" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1142" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1142" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1143" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1143" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1143" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1143" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1143" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1143" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1143" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1144" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1144" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1144" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1144" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1144" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1144" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1144" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1145" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1145" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1145" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1145" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1145" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1145" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1145" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1146" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1146" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1146" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1146" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1146" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1146" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1146" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1147" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1147" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1147" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1147" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1147" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1147" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1147" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1148" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1148" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1148" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1148" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1148" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1148" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1148" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1149" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1149" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1149" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1149" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1149" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1149" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1149" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1150" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1150" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1150" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1150" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1150" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1150" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1150" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1151" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1151" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1151" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1151" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1151" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1151" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1151" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1152" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1152" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1152" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1152" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1152" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1152" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1152" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1153" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1153" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1153" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1153" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1153" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1153" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1153" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1154" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1154" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1154" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1154" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1154" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1154" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1154" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1155" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1155" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1155" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1155" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1155" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1155" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1155" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1156" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1156" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1156" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1156" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1156" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1156" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1156" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1157" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1157" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1157" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1157" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1157" t="s">
+        <v>517</v>
+      </c>
+      <c r="F1157" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1157" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1158" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1158" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1158" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1158" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1158" t="s">
+        <v>517</v>
+      </c>
+      <c r="F1158" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1158" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1159" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1159" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1159" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1159" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1159" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1159" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1159" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1160" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1160" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1160" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1160" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1160" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1160" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1160" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1161" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1161" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1161" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1161" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1161" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1162" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1162" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1162" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1162" t="s">
+        <v>627</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>934</v>
+      </c>
+      <c r="G1162" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1163" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1163" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1163" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1163" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1163" t="s">
+        <v>478</v>
+      </c>
+      <c r="F1163" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1163" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1164" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1164" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1164" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1164" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1164" t="s">
+        <v>495</v>
+      </c>
+      <c r="F1164" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1164" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1165" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1165" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1165" t="s">
+        <v>495</v>
+      </c>
+      <c r="F1165" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1165" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1166" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1166" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1166" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1166" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1166" t="s">
+        <v>495</v>
+      </c>
+      <c r="F1166" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1166" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1167" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1167" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1167" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1167" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1167" t="s">
+        <v>495</v>
+      </c>
+      <c r="F1167" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1167" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1168" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1168" t="s">
+        <v>762</v>
+      </c>
+      <c r="C1168" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1168" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1168" t="s">
+        <v>495</v>
+      </c>
+      <c r="F1168" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1168" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1169" t="s">
+        <v>765</v>
+      </c>
+      <c r="B1169" t="s">
+        <v>764</v>
+      </c>
+      <c r="C1169" t="s">
+        <v>766</v>
+      </c>
+      <c r="D1169" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1169" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1169" t="s">
+        <v>763</v>
+      </c>
+      <c r="G1169" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1170" t="s">
+        <v>983</v>
+      </c>
+      <c r="B1170" t="s">
+        <v>769</v>
+      </c>
+      <c r="C1170" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1170" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1170" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1170" t="s">
+        <v>768</v>
+      </c>
+      <c r="G1170" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1171" t="s">
+        <v>773</v>
+      </c>
+      <c r="B1171" t="s">
+        <v>774</v>
+      </c>
+      <c r="C1171" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1171" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1171" t="s">
+        <v>770</v>
+      </c>
+      <c r="F1171" t="s">
+        <v>771</v>
+      </c>
+      <c r="G1171" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1172" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1172" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1172" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1172" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1172" t="s">
+        <v>491</v>
+      </c>
+      <c r="F1172" t="s">
+        <v>938</v>
+      </c>
+      <c r="G1172" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1173" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1173" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1173" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1173" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1173" t="s">
+        <v>937</v>
+      </c>
+      <c r="F1173" t="s">
+        <v>939</v>
+      </c>
+      <c r="G1173" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1174" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1174" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1174" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1174" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1174" t="s">
+        <v>494</v>
+      </c>
+      <c r="F1174" t="s">
+        <v>940</v>
+      </c>
+      <c r="G1174" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1175" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1175" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1175" t="s">
+        <v>728</v>
+      </c>
+      <c r="D1175" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1175" t="s">
+        <v>941</v>
+      </c>
+      <c r="F1175" t="s">
+        <v>942</v>
+      </c>
+      <c r="G1175" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1176" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1176" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1176" t="s">
+        <v>693</v>
+      </c>
+      <c r="D1176" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1176" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1176" t="s">
+        <v>940</v>
+      </c>
+      <c r="G1176" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1177" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1177" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1177" t="s">
+        <v>693</v>
+      </c>
+      <c r="D1177" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1177" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1177" t="s">
+        <v>940</v>
+      </c>
+      <c r="G1177" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1178" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1178" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1178" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1178" t="s">
+        <v>944</v>
+      </c>
+      <c r="F1178" t="s">
+        <v>955</v>
+      </c>
+      <c r="G1178" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1179" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1179" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1179" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1179" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1179" t="s">
+        <v>956</v>
+      </c>
+      <c r="G1179" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1180" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1180" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1180" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1180" t="s">
+        <v>945</v>
+      </c>
+      <c r="F1180" t="s">
+        <v>957</v>
+      </c>
+      <c r="G1180" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1181" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1181" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1181" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1181" t="s">
+        <v>946</v>
+      </c>
+      <c r="F1181" t="s">
+        <v>955</v>
+      </c>
+      <c r="G1181" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1182" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1182" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1182" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1182" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1182" t="s">
+        <v>958</v>
+      </c>
+      <c r="G1182" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1183" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1183" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1183" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1183" t="s">
+        <v>945</v>
+      </c>
+      <c r="F1183" t="s">
+        <v>502</v>
+      </c>
+      <c r="G1183" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1184" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1184" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1184" t="s">
+        <v>947</v>
+      </c>
+      <c r="F1184" t="s">
+        <v>502</v>
+      </c>
+      <c r="G1184" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1185" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1185" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>948</v>
+      </c>
+      <c r="F1185" t="s">
+        <v>956</v>
+      </c>
+      <c r="G1185" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1186" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1186" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>949</v>
+      </c>
+      <c r="F1186" t="s">
+        <v>959</v>
+      </c>
+      <c r="G1186" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1187" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1187" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>455</v>
+      </c>
+      <c r="F1187" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1187" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1188" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1188" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1188" t="s">
+        <v>949</v>
+      </c>
+      <c r="F1188" t="s">
+        <v>960</v>
+      </c>
+      <c r="G1188" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1189" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1189" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1189" t="s">
+        <v>945</v>
+      </c>
+      <c r="F1189" t="s">
+        <v>961</v>
+      </c>
+      <c r="G1189" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1190" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1190" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1190" t="s">
+        <v>944</v>
+      </c>
+      <c r="F1190" t="s">
+        <v>962</v>
+      </c>
+      <c r="G1190" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1191" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1191" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>409</v>
+      </c>
+      <c r="F1191" t="s">
+        <v>502</v>
+      </c>
+      <c r="G1191" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1192" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1192" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1192" t="s">
+        <v>519</v>
+      </c>
+      <c r="F1192" t="s">
+        <v>963</v>
+      </c>
+      <c r="G1192" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1193" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1193" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1193" t="s">
+        <v>950</v>
+      </c>
+      <c r="F1193" t="s">
+        <v>964</v>
+      </c>
+      <c r="G1193" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1194" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1194" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1194" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1194" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1194" t="s">
+        <v>502</v>
+      </c>
+      <c r="G1194" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1195" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1195" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1195" t="s">
+        <v>951</v>
+      </c>
+      <c r="F1195" t="s">
+        <v>964</v>
+      </c>
+      <c r="G1195" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1196" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1196" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1196" t="s">
+        <v>514</v>
+      </c>
+      <c r="F1196" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1196" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1197" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1197" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1197" t="s">
+        <v>946</v>
+      </c>
+      <c r="F1197" t="s">
+        <v>956</v>
+      </c>
+      <c r="G1197" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1198" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1198" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>952</v>
+      </c>
+      <c r="F1198" t="s">
+        <v>659</v>
+      </c>
+      <c r="G1198" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1199" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1199" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1199" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>953</v>
+      </c>
+      <c r="F1199" t="s">
+        <v>659</v>
+      </c>
+      <c r="G1199" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1200" t="s">
+        <v>776</v>
+      </c>
+      <c r="B1200" t="s">
+        <v>777</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1200" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>513</v>
+      </c>
+      <c r="F1200" t="s">
+        <v>964</v>
+      </c>
+      <c r="G1200" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1201" t="s">
+        <v>981</v>
+      </c>
+      <c r="B1201" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1201" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1201" t="s">
+        <v>778</v>
+      </c>
+      <c r="G1201" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1202" t="s">
+        <v>781</v>
+      </c>
+      <c r="B1202" t="s">
+        <v>782</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>780</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>967</v>
+      </c>
+      <c r="F1202" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1202" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1203" t="s">
+        <v>781</v>
+      </c>
+      <c r="B1203" t="s">
+        <v>782</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>780</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>968</v>
+      </c>
+      <c r="F1203" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1203" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1204" t="s">
+        <v>781</v>
+      </c>
+      <c r="B1204" t="s">
+        <v>782</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>780</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>811</v>
+      </c>
+      <c r="F1204" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1205" t="s">
+        <v>781</v>
+      </c>
+      <c r="B1205" t="s">
+        <v>782</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>780</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>969</v>
+      </c>
+      <c r="F1205" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1205" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1206" t="s">
+        <v>781</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>782</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>780</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>343</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1206" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1207" t="s">
+        <v>984</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>669</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1207" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1208" t="s">
+        <v>985</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>895</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>896</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1208" s="10" t="s">
+        <v>897</v>
+      </c>
+      <c r="G1208" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1209" t="s">
+        <v>985</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>895</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>896</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>898</v>
+      </c>
+      <c r="F1209" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1209" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1210" t="s">
+        <v>985</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>895</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>896</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>899</v>
+      </c>
+      <c r="F1210" s="10" t="s">
+        <v>900</v>
+      </c>
+      <c r="G1210" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1211" t="s">
+        <v>784</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>787</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>669</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>783</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1211" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1212" t="s">
+        <v>785</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>786</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>612</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>789</v>
+      </c>
+      <c r="G1212" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1213" t="s">
+        <v>791</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>792</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>788</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>612</v>
+      </c>
+      <c r="F1213" t="s">
+        <v>793</v>
+      </c>
+      <c r="G1213" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1214" t="s">
+        <v>982</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>971</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>795</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>796</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1214" t="s">
+        <v>800</v>
+      </c>
+      <c r="G1214" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1215" t="s">
+        <v>982</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>971</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>795</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>797</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>798</v>
+      </c>
+      <c r="F1215" t="s">
+        <v>800</v>
+      </c>
+      <c r="G1215" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1216" t="s">
+        <v>802</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>801</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>389</v>
+      </c>
+      <c r="F1216" t="s">
+        <v>804</v>
+      </c>
+      <c r="G1216" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1217" t="s">
+        <v>805</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>806</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>807</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1217" t="s">
+        <v>808</v>
+      </c>
+      <c r="G1217" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1218" t="s">
+        <v>810</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>766</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1218" t="s">
+        <v>234</v>
+      </c>
+      <c r="F1218" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1218" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1219" t="s">
+        <v>810</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>766</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1219" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1219" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1219" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1220" t="s">
+        <v>810</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>766</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1220" t="s">
+        <v>811</v>
+      </c>
+      <c r="F1220" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1220" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1221" t="s">
+        <v>816</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>818</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>815</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1221" t="s">
+        <v>813</v>
+      </c>
+      <c r="F1221" t="s">
+        <v>656</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1222" t="s">
+        <v>821</v>
+      </c>
+      <c r="B1222" t="s">
+        <v>820</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>672</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1222" t="s">
+        <v>351</v>
+      </c>
+      <c r="F1222" t="s">
+        <v>819</v>
+      </c>
+      <c r="G1222" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1223" t="s">
+        <v>823</v>
+      </c>
+      <c r="B1223" t="s">
+        <v>824</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>974</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1223" t="s">
+        <v>973</v>
+      </c>
+      <c r="F1223" t="s">
+        <v>656</v>
+      </c>
+      <c r="G1223" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1224" t="s">
+        <v>823</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>824</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1224" t="s">
+        <v>491</v>
+      </c>
+      <c r="F1224" t="s">
+        <v>975</v>
+      </c>
+      <c r="G1224" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1225" t="s">
+        <v>823</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>824</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>685</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1225" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1225" t="s">
+        <v>975</v>
+      </c>
+      <c r="G1225" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1226" t="s">
+        <v>823</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>824</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>693</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>975</v>
+      </c>
+      <c r="G1226" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1227" t="s">
+        <v>823</v>
+      </c>
+      <c r="B1227" t="s">
+        <v>824</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>693</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1227" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1227" t="s">
+        <v>975</v>
+      </c>
+      <c r="G1227" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1228" t="s">
+        <v>931</v>
+      </c>
+      <c r="B1228" t="s">
+        <v>828</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>903</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>825</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>826</v>
+      </c>
+      <c r="F1228" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1228" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1229" t="s">
+        <v>931</v>
+      </c>
+      <c r="B1229" t="s">
+        <v>828</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>825</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>827</v>
+      </c>
+      <c r="F1229" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1229" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1230" t="s">
+        <v>829</v>
+      </c>
+      <c r="B1230" t="s">
+        <v>830</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>779</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1230" t="s">
+        <v>831</v>
+      </c>
+      <c r="G1230" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1231" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1231" t="s">
+        <v>833</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>838</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>834</v>
+      </c>
+      <c r="F1231" t="s">
+        <v>835</v>
+      </c>
+      <c r="G1231" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1232" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1232" t="s">
+        <v>837</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>838</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>834</v>
+      </c>
+      <c r="F1232" t="s">
+        <v>840</v>
+      </c>
+      <c r="G1232" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1233" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1233" t="s">
+        <v>837</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>845</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>841</v>
+      </c>
+      <c r="F1233" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1233" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1234" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1234" t="s">
+        <v>837</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>846</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>842</v>
+      </c>
+      <c r="F1234" t="s">
+        <v>595</v>
+      </c>
+      <c r="G1234" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1235" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1235" t="s">
+        <v>837</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>843</v>
+      </c>
+      <c r="F1235" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1235" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1236" t="s">
+        <v>836</v>
+      </c>
+      <c r="B1236" t="s">
+        <v>837</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>558</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>561</v>
+      </c>
+      <c r="F1236" t="s">
+        <v>844</v>
+      </c>
+      <c r="G1236" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1237" t="s">
+        <v>847</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>848</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>851</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>561</v>
+      </c>
+      <c r="F1237" t="s">
+        <v>850</v>
+      </c>
+      <c r="G1237" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1238" t="s">
+        <v>852</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>853</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>854</v>
+      </c>
+      <c r="F1238" t="s">
+        <v>855</v>
+      </c>
+      <c r="G1238" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1239" t="s">
+        <v>858</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>857</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1239" t="s">
+        <v>860</v>
+      </c>
+      <c r="G1239" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1240" t="s">
+        <v>932</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>861</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>863</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1240" t="s">
+        <v>862</v>
+      </c>
+      <c r="G1240" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1241" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>867</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>865</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1241" t="s">
+        <v>869</v>
+      </c>
+      <c r="G1241" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1242" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>867</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>865</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1242" t="s">
+        <v>869</v>
+      </c>
+      <c r="G1242" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1243" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>867</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>865</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>313</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1243" t="s">
+        <v>869</v>
+      </c>
+      <c r="G1243" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1244" t="s">
+        <v>870</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>871</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>872</v>
+      </c>
+      <c r="F1244" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1244" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1245" t="s">
+        <v>873</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>874</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>670</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>875</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1245" t="s">
+        <v>876</v>
+      </c>
+      <c r="G1245" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1246" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>878</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>879</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>881</v>
+      </c>
+      <c r="F1246" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1246" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1247" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>878</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>879</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>882</v>
+      </c>
+      <c r="E1247" s="10" t="s">
+        <v>881</v>
+      </c>
+      <c r="F1247" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1247" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1248" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>878</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>879</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>883</v>
+      </c>
+      <c r="E1248" s="10" t="s">
+        <v>884</v>
+      </c>
+      <c r="F1248" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1248" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1249" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>878</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>879</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1249" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F1249" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1249" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1250" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>878</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>879</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1250" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="F1250" t="s">
+        <v>604</v>
+      </c>
+      <c r="G1250" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1251" t="s">
+        <v>885</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>886</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>890</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1251" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="F1251" t="s">
+        <v>892</v>
+      </c>
+      <c r="G1251" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1252" t="s">
+        <v>888</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>889</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>890</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1252" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="F1252" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1252" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1253" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>894</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>977</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>976</v>
+      </c>
+      <c r="E1253" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F1253" s="10" t="s">
+        <v>978</v>
+      </c>
+      <c r="G1253" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1254" t="s">
+        <v>901</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>902</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>903</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1254" s="10" t="s">
+        <v>904</v>
+      </c>
+      <c r="G1254" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1255" t="s">
+        <v>906</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>905</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1255" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1255" s="10" t="s">
+        <v>908</v>
+      </c>
+      <c r="G1255" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1256" t="s">
+        <v>986</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>909</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>668</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1256" t="s">
+        <v>317</v>
+      </c>
+      <c r="F1256" s="10" t="s">
+        <v>910</v>
+      </c>
+      <c r="G1256" s="10" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1257" t="s">
+        <v>911</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>912</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>617</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>913</v>
+      </c>
+      <c r="F1257" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="G1257" s="10" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1258" t="s">
+        <v>911</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>912</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>617</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>914</v>
+      </c>
+      <c r="E1258" t="s">
+        <v>915</v>
+      </c>
+      <c r="F1258" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="G1258" s="10" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1259" t="s">
+        <v>917</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>918</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>919</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>921</v>
+      </c>
+      <c r="F1259" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1259" s="10" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1260" t="s">
+        <v>917</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>918</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>919</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1260" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1260" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1260" s="10" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1261" t="s">
+        <v>917</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>918</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>919</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1261" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1261" s="10" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1262" t="s">
+        <v>923</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>924</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>930</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>922</v>
+      </c>
+      <c r="F1262" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="G1262" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1263" t="s">
+        <v>926</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>927</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>925</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1263" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1263" s="10" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1264" t="s">
+        <v>928</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>929</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>930</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1264" t="s">
+        <v>922</v>
+      </c>
+      <c r="F1264" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1264" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Saprotrophs.xlsx
+++ b/Saprotrophs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaseamus/Desktop/PhD/Papers/Microbial decomposition/microdeco/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232EA0A3-F321-4C4C-81B6-3CFA4E8C3DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF85A62-269B-DB46-A9CA-BFD50937A813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19020" xr2:uid="{66FE6731-E709-924C-9370-CCE9A242822C}"/>
+    <workbookView xWindow="6040" yWindow="500" windowWidth="28320" windowHeight="19020" xr2:uid="{66FE6731-E709-924C-9370-CCE9A242822C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8848" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8876" uniqueCount="999">
   <si>
     <t>Reference</t>
   </si>
@@ -2997,6 +2997,42 @@
   </si>
   <si>
     <t>Koch et al. 2019b</t>
+  </si>
+  <si>
+    <t>Saha &amp; Weinberger 2019</t>
+  </si>
+  <si>
+    <t>10.1111/1365-2745.13193</t>
+  </si>
+  <si>
+    <t>Agarophyton vermiculophyllum</t>
+  </si>
+  <si>
+    <t>Croceitalea</t>
+  </si>
+  <si>
+    <t>eckloniae</t>
+  </si>
+  <si>
+    <t>Kordia</t>
+  </si>
+  <si>
+    <t>algicida</t>
+  </si>
+  <si>
+    <t>Figure 1, Table 1</t>
+  </si>
+  <si>
+    <t>Zhu et al. 2017</t>
+  </si>
+  <si>
+    <t>10.1111/1462-2920.13699</t>
+  </si>
+  <si>
+    <t>Figure 4, 5</t>
+  </si>
+  <si>
+    <t>alginate, Laminaria digitata</t>
   </si>
 </sst>
 </file>
@@ -3420,7 +3456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B2102F-A492-4646-A482-3DC7C29DBCFC}">
-  <dimension ref="A1:AB1264"/>
+  <dimension ref="A1:AB1268"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" customWidth="1"/>
@@ -3428,7 +3464,7 @@
     <col min="3" max="3" width="23.6640625" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" customWidth="1"/>
-    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="6" max="6" width="66.33203125" customWidth="1"/>
     <col min="10" max="10" width="20.33203125" customWidth="1"/>
     <col min="19" max="19" width="15.83203125" customWidth="1"/>
   </cols>
@@ -38659,6 +38695,98 @@
         <v>68</v>
       </c>
     </row>
+    <row r="1265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1265" t="s">
+        <v>987</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>988</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>989</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>514</v>
+      </c>
+      <c r="F1265" t="s">
+        <v>989</v>
+      </c>
+      <c r="G1265" s="10" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1266" t="s">
+        <v>987</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>988</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>989</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>990</v>
+      </c>
+      <c r="E1266" t="s">
+        <v>991</v>
+      </c>
+      <c r="F1266" t="s">
+        <v>989</v>
+      </c>
+      <c r="G1266" s="10" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1267" t="s">
+        <v>987</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>988</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>989</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>992</v>
+      </c>
+      <c r="E1267" t="s">
+        <v>993</v>
+      </c>
+      <c r="F1267" t="s">
+        <v>989</v>
+      </c>
+      <c r="G1267" s="10" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1268" t="s">
+        <v>995</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>996</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1268" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1268" t="s">
+        <v>998</v>
+      </c>
+      <c r="G1268" s="10" t="s">
+        <v>997</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
